--- a/per-stock/PLAB/financials.xlsx
+++ b/per-stock/PLAB/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2949498880</v>
+        <v>1982949120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2751180032</v>
+        <v>1801357184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.37607</v>
+        <v>12.409595</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.194916</v>
+        <v>16.607407</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4208114</v>
+        <v>2.302622</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.35141</v>
+        <v>0.33773997</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24375</v>
+        <v>0.20091</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1583</v>
+        <v>0.1847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.12222999</v>
+        <v>0.13239999</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.061</v>
+        <v>-0.005</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>636870976</v>
+        <v>637667008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21000</v>
+        <v>3864000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>36507248</v>
+        <v>96245000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58966394</v>
+        <v>58963698</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>50.02</v>
+        <v>33.63</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D37</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C37</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B37</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B37:E37)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1718,7 +2186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1744,27 +2212,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1780,19 +2248,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>1549662.321747</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2482945</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>3909150</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-3535984</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-5942201</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>4518535</v>
+        <v>-5939268.784872</v>
       </c>
       <c r="G2" s="3" t="n"/>
     </row>
@@ -1803,19 +2271,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.196933</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.193</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.248</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.191</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>0.245</v>
+        <v>0.190906</v>
       </c>
       <c r="G3" s="3" t="n"/>
     </row>
@@ -1826,19 +2294,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>65998000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>81470000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>75721000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>71839000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>80640000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>79554000</v>
       </c>
       <c r="G4" s="3" t="n"/>
     </row>
@@ -1849,19 +2317,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>7869000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>12865000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>18615000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-14258000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-31111000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>18443000</v>
       </c>
       <c r="G5" s="3" t="n"/>
     </row>
@@ -1872,19 +2340,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>7869000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>12865000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>18615000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-14258000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-31111000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>18443000</v>
       </c>
       <c r="G6" s="3" t="n"/>
     </row>
@@ -1895,19 +2363,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>31429000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>42939000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>61801000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>22891000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>8861000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>42851000</v>
       </c>
       <c r="G7" s="3" t="n"/>
     </row>
@@ -1918,19 +2386,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>20010000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>19802000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>18371000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>18848000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>19594000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>20792000</v>
       </c>
       <c r="G8" s="3" t="n"/>
     </row>
@@ -1941,19 +2409,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>144183000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>146364000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>140236000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>139539000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>133086000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>136603000</v>
       </c>
       <c r="G9" s="3" t="n"/>
     </row>
@@ -1964,19 +2432,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>73867000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>94335000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>94336000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>57581000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>49529000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>97997000</v>
       </c>
       <c r="G10" s="3" t="n"/>
     </row>
@@ -1987,19 +2455,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>53857000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>74533000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>75965000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>38733000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>29935000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>77205000</v>
       </c>
       <c r="G11" s="3" t="n"/>
     </row>
@@ -2010,19 +2478,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>3808000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>6808000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>5240000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>4830000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>5325000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>6538000</v>
       </c>
       <c r="G12" s="3" t="n"/>
     </row>
@@ -2036,16 +2504,16 @@
         <v>1000</v>
       </c>
       <c r="C13" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>4000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>47000</v>
       </c>
       <c r="G13" s="3" t="n"/>
     </row>
@@ -2056,19 +2524,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>3809000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>6809000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>5243000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>4830000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>5329000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>6585000</v>
       </c>
       <c r="G14" s="3" t="n"/>
     </row>
@@ -2079,19 +2547,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>25109662.321747</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>32556945</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>47095150</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>33613016</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>34029799</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>28926535</v>
+        <v>34032731.215128</v>
       </c>
       <c r="G15" s="3" t="n"/>
     </row>
@@ -2102,19 +2570,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>31429000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>42939000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>61801000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>22891000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>8861000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>42851000</v>
       </c>
       <c r="G16" s="3" t="n"/>
     </row>
@@ -2125,19 +2593,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>167761000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>170207000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>163663000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>162233000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>155275000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>159961000</v>
       </c>
       <c r="G17" s="3" t="n"/>
     </row>
@@ -2148,19 +2616,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>42179000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>54859000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>52107000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>48161000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>55717000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>52177000</v>
       </c>
       <c r="G18" s="3" t="n"/>
     </row>
@@ -2171,19 +2639,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>58745000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>58390000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>57977000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>58068000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>60974000</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>62661000</v>
       </c>
       <c r="G19" s="3" t="n"/>
     </row>
@@ -2194,19 +2662,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>58123000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>57794000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>57600000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>57937000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>60793000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>62093000</v>
       </c>
       <c r="G20" s="3" t="n"/>
     </row>
@@ -2217,19 +2685,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.15</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0.68</v>
       </c>
       <c r="G21" s="3" t="n"/>
     </row>
@@ -2240,19 +2708,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>1.07</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>0.15</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.6899999999999999</v>
       </c>
       <c r="G22" s="3" t="n"/>
     </row>
@@ -2263,19 +2731,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>31429000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>42939000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>61801000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>22891000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>8861000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>42851000</v>
       </c>
       <c r="G23" s="3" t="n"/>
     </row>
@@ -2301,19 +2769,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>31429000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>42939000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>61801000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>22891000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>8861000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>42851000</v>
       </c>
       <c r="G25" s="3" t="n"/>
     </row>
@@ -2324,19 +2792,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>31429000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>42939000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>61801000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>22891000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>8861000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>42851000</v>
       </c>
       <c r="G26" s="3" t="n"/>
     </row>
@@ -2347,19 +2815,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-11821000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-17238000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-16820000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-6248000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-15356000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>-15406000</v>
       </c>
       <c r="G27" s="3" t="n"/>
     </row>
@@ -2370,19 +2838,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>43250000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>60177000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>78621000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>29139000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>24217000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>58257000</v>
       </c>
       <c r="G28" s="3" t="n"/>
     </row>
@@ -2393,19 +2861,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>43250000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>60177000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>78621000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>29139000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>24217000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>58257000</v>
       </c>
       <c r="G29" s="3" t="n"/>
     </row>
@@ -2416,19 +2884,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>10606000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>14355000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-2659000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>9594000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>5714000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>18901000</v>
       </c>
       <c r="G30" s="3" t="n"/>
     </row>
@@ -2439,19 +2907,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>53856000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>74532000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>75962000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>38733000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>29931000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>77158000</v>
       </c>
       <c r="G31" s="3" t="n"/>
     </row>
@@ -2462,19 +2930,19 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>7869000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>12865000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>18615000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-14258000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-31111000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>18443000</v>
       </c>
       <c r="G32" s="3" t="n"/>
     </row>
@@ -2485,19 +2953,19 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>7869000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>12865000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>18615000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-14258000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-31111000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>18443000</v>
       </c>
       <c r="G33" s="3" t="n"/>
     </row>
@@ -2508,19 +2976,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>3808000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>6808000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>5240000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>4830000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>5325000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>6538000</v>
       </c>
       <c r="G34" s="3" t="n"/>
     </row>
@@ -2534,16 +3002,16 @@
         <v>1000</v>
       </c>
       <c r="C35" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D35" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>4000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>47000</v>
       </c>
       <c r="G35" s="3" t="n"/>
     </row>
@@ -2554,19 +3022,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>3809000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>6809000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>5243000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>4830000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>5329000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>6585000</v>
       </c>
       <c r="G36" s="3" t="n"/>
     </row>
@@ -2577,19 +3045,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>42179000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>54859000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>52107000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>48161000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>55717000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>52177000</v>
       </c>
       <c r="G37" s="3" t="n"/>
     </row>
@@ -2600,19 +3068,19 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>23578000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>23843000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>23427000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>22694000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>22189000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>23358000</v>
       </c>
       <c r="G38" s="3" t="n"/>
     </row>
@@ -2622,10 +3090,10 @@
           <t>Other Operating Expenses</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n">
         <v>-56000</v>
       </c>
-      <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
@@ -2640,19 +3108,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>2822000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>2588000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>3186000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>4271000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>4090000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>4257000</v>
       </c>
       <c r="G40" s="3" t="n"/>
     </row>
@@ -2663,19 +3131,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>20756000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>21311000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>20001000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>18423000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>18099000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>19101000</v>
       </c>
       <c r="G41" s="3" t="n"/>
     </row>
@@ -2686,19 +3154,19 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>65757000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>78702000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>75534000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>70855000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>77906000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>75535000</v>
       </c>
       <c r="G42" s="3" t="n"/>
     </row>
@@ -2709,19 +3177,19 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>144183000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>146364000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>140236000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>139539000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>133086000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>136603000</v>
       </c>
       <c r="G43" s="3" t="n"/>
     </row>
@@ -2732,19 +3200,19 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>209940000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>225066000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>215770000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>210394000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>210992000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>212138000</v>
       </c>
       <c r="G44" s="3" t="n"/>
     </row>
@@ -2755,19 +3223,19 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>209940000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>225066000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>215770000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>210394000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>210992000</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>212138000</v>
       </c>
       <c r="G45" s="3" t="n"/>
     </row>
@@ -2776,7 +3244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4396,7 +4864,1841 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>58152000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>58108000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>57633000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>57587000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>58711000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>58152000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>58108000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>57633000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>57587000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>58711000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3864000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>5959000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1241250000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1211390000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1173589000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1125551000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1100920000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1241250000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1211411000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1173589000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1125551000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1100920000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>756961000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>739600000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>724179000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>697311000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>689023000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1241250000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1211390000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1173589000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1125551000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1100920000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3864000</v>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n">
+        <v>5959000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>2652000</v>
+      </c>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1241250000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1211390000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1173589000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1125551000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1100920000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1241250000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1211400000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1173589000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1125551000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1100920000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1693461000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1649921000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1597307000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1538000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1496769000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>452211000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>438531000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>423718000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>412449000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>395849000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1241250000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1211390000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1173589000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1125551000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1100920000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-97949000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-92320000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-86120000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-68504000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-87295000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-97949000</v>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>-86120000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-68504000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-87295000</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-120325000</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>845752000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>814323000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>772199000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>710398000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>698423000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>492865000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>488806000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>486934000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>483081000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>489205000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>582000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>581000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>576000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>576000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>587000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>582000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>581000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>576000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>576000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>587000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>237365000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>251498000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>207227000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>214765000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>206263000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>44849000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>41354000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>39840000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>39480000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46547000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>44839000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>14592000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>39824000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>39461000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>13218000</v>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n">
+        <v>12993000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
+        <v>13218000</v>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n">
+        <v>12993000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>4530000</v>
+      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n">
+        <v>4310000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>5041000</v>
+      </c>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n">
+        <v>8910000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n">
+        <v>5041000</v>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n">
+        <v>8910000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>3853000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>3973000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>3853000</v>
+      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>3973000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>186965000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>206649000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>165873000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>174925000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>166783000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
+        <v>9491000</v>
+      </c>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
+        <v>12375000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
+        <v>9491000</v>
+      </c>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n">
+        <v>12375000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1986000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>1986000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>2631000</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>26284000</v>
+      </c>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n">
+        <v>31188000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>186954000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>206638000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>128112000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>174914000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>166772000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>78984000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>94987000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>19010000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>74563000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>77288000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>107970000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>111651000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>109102000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>100351000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>89484000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
+        <v>24893000</v>
+      </c>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n">
+        <v>27037000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n">
+        <v>21094000</v>
+      </c>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n">
+        <v>24200000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>107970000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>111651000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>84209000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>100351000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>89484000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1930826000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1901419000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1804534000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1752765000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1703032000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>986900000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>955170000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>914482000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>880529000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>847226000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>21575000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>22295000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>19839000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>15122000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>14941000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>37389000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>38255000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>40207000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>26419000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>24727000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>37389000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>38255000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>40207000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>26419000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>24727000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>927936000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>894620000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>854436000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>838988000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>807558000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>-1656453000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>-1644384000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>-1634873000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-1657948000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-1616788000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>2584389000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>2539004000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2489309000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2496936000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2424346000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>20006000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>20063000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>20474000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>21037000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>20324000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>147482000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>167882000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>134880000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>108743000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>122474000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>2198163000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>2140203000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>2128850000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2162233000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2080102000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>202576000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>198547000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>192860000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>192625000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>189230000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>12262000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>12309000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>12245000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>12298000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>12216000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>943926000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>946249000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>890052000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>872236000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>855806000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>49482000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>47235000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>4636000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>42073000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>40221000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="n">
+        <v>12889000</v>
+      </c>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n">
+        <v>7645000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>67826000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>62653000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>61767000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>63490000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>61201000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1959000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1616000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1239000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>65864000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>60768000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>60150000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>61908000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>59938000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>188951000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>199490000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>222595000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>190875000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>195977000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Receivables Adjustments Allowances</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n">
+        <v>-1171000</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>-1104000</v>
+      </c>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n">
+        <v>12670000</v>
+      </c>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n">
+        <v>31737000</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>39831000</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>11532000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n">
+        <v>14004000</v>
+      </c>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n">
+        <v>7684000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>188951000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>199490000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>195921000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>190875000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>165411000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>-1142000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>-1153000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>-1166000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-1184000</v>
+      </c>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n">
+        <v>-1126000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>190093000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>200643000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>197087000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>192059000</v>
+      </c>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n">
+        <v>201956000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>637667000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>636871000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>588165000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>575798000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>558407000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>126177000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>92738000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>95909000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>96277000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>27699000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>511490000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>544133000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>492256000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>479521000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>530708000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>306531000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>306784000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>270090000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>308375000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>341978000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>204959000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>237349000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>222166000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>171146000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>188730000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5422,13 +7724,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5437,6 +7739,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5447,25 +7750,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
@@ -5478,20 +7786,21 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>1229000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>49619000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>20181000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>25216000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-29096000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>43266000</v>
-      </c>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5506,14 +7815,15 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>-20740000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-72109000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-4573000</v>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5522,7 +7832,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-3000</v>
@@ -5531,11 +7841,12 @@
         <v>-3000</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>-2623000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-15343000</v>
-      </c>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5544,20 +7855,21 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-45801000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-47635000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-67643000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-24839000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-60549000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-35200000</v>
-      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5566,20 +7878,21 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>511490000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>544133000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>492256000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>479521000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>530708000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>642200000</v>
-      </c>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5588,20 +7901,21 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-82000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-2792000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>85000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-104000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-164000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-2674000</v>
-      </c>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5610,20 +7924,21 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>544133000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>495113000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>479521000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>530708000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>642200000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>601243000</v>
-      </c>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5632,20 +7947,21 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-807000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>-5915000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>-9901000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>11826000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>19505000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>-21202000</v>
-      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5654,20 +7970,21 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-31754000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>57727000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>22551000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-62909000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-130833000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>64833000</v>
-      </c>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5676,20 +7993,21 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-1170000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>749000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-20212000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-74594000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-20478000</v>
-      </c>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5698,20 +8016,21 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-1170000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>749000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-20212000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-74594000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-20478000</v>
-      </c>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5720,16 +8039,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>464000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>752000</v>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n">
         <v>537000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>150000</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="G13" s="3" t="n">
         <v>1433000</v>
       </c>
     </row>
@@ -5740,20 +8062,21 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-1632000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>2150000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-6000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-12000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-1995000</v>
-      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5768,14 +8091,15 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>-20740000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-72109000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-4573000</v>
-      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5790,14 +8114,15 @@
         <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>-20740000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-72109000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-4573000</v>
-      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5806,7 +8131,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-3000</v>
@@ -5815,11 +8140,12 @@
         <v>-3000</v>
       </c>
       <c r="E17" s="3" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>-2623000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-15343000</v>
-      </c>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5828,7 +8154,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>-3000</v>
@@ -5837,11 +8163,12 @@
         <v>-3000</v>
       </c>
       <c r="E18" s="3" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>-2623000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-15343000</v>
-      </c>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5850,7 +8177,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>-3000</v>
@@ -5859,11 +8186,12 @@
         <v>-3000</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>-2623000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-15343000</v>
-      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5872,20 +8200,21 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-77614000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-40276000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-65300000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-92752000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-87692000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>6845000</v>
-      </c>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5894,20 +8223,21 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-77614000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-40276000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-65300000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-92752000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-87692000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>6845000</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5916,20 +8246,21 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>2487000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>746000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>303000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>546000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>563000</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5938,20 +8269,21 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-31821000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>4872000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>1597000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-68216000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-27689000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>41482000</v>
-      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5960,20 +8292,21 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>37399000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>41483000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>34675000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>666000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>41482000</v>
-      </c>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5982,20 +8315,21 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-69220000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-36611000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-33078000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-68882000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-27689000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6004,20 +8338,21 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-45801000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-47635000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-67549000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-24839000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-60549000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-35200000</v>
-      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6026,20 +8361,21 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-45801000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-47635000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-67549000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-24839000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-60549000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-35200000</v>
-      </c>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6048,20 +8384,21 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>47030000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>97254000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>87824000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>50055000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>31453000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>78466000</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6070,20 +8407,21 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>47030000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>97254000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>87824000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>50055000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>31453000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>78466000</v>
-      </c>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6092,20 +8430,21 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-19955000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>14424000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>4615000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-1225000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-15734000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-3917000</v>
-      </c>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6114,20 +8453,21 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>221000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-2187000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>3292000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-1075000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-6410000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-522000</v>
-      </c>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6136,20 +8476,21 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-26354000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>20136000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>6240000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-6835000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-3587000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-8731000</v>
-      </c>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6158,20 +8499,21 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-26354000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>20136000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>6240000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-6835000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-3587000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-8731000</v>
-      </c>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6180,20 +8522,21 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-26354000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>20136000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>6240000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-6835000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-3587000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-8731000</v>
-      </c>
+      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6202,20 +8545,21 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-5268000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-982000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>1152000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-1400000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-2161000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-2533000</v>
-      </c>
+      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6224,20 +8568,21 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>11446000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-2543000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-6069000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>8085000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-3576000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>7869000</v>
-      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6246,20 +8591,21 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>11446000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-2543000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-6069000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>8085000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-3576000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>7869000</v>
-      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6268,20 +8614,21 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>3725000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>2851000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>3385000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>3293000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>3376000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>3334000</v>
-      </c>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6290,20 +8637,21 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>20010000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>19802000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>18371000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>18848000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>19594000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>20792000</v>
-      </c>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6312,20 +8660,21 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>20010000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>19802000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>18371000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>18848000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>19594000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>20792000</v>
-      </c>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6334,27 +8683,28 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>43250000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>60177000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>78621000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>29139000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>24217000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>58257000</v>
-      </c>
+      <c r="G41" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6382,12 +8732,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>'Net Debt' not found in statements — left blank</t>
         </is>
       </c>
     </row>
